--- a/Datos Tesis Upstream/Algoritmos y Programacion/2425-2/Partic.Alg 2425-2 Secc. 2.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2425-2/Partic.Alg 2425-2 Secc. 2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Algoritmos y Programacion/2425-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13FA2AC-825C-2943-B901-3AAD83714D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720D7A40-DECD-684A-AC4C-A84F4029870D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15980" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista" sheetId="1" r:id="rId1"/>
@@ -572,7 +572,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{E5F06E05-4895-6E45-B5A8-6B7CFFC78FA5}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{E5F06E05-4895-6E45-B5A8-6B7CFFC78FA5}">
       <text>
         <r>
           <rPr>
@@ -587,7 +587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{EA976860-6149-1C4E-B1D9-8FDDBA24AA83}">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{EA976860-6149-1C4E-B1D9-8FDDBA24AA83}">
       <text>
         <r>
           <rPr>
@@ -602,7 +602,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{8E83DC64-019A-3847-BE5D-50F7C9FBB96C}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{8E83DC64-019A-3847-BE5D-50F7C9FBB96C}">
       <text>
         <r>
           <rPr>
@@ -617,7 +617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{F716F9BC-4D2C-B84F-8E9F-98BE760DD05D}">
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{F716F9BC-4D2C-B84F-8E9F-98BE760DD05D}">
       <text>
         <r>
           <rPr>
@@ -632,7 +632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S12" authorId="0" shapeId="0" xr:uid="{A5A840E0-3932-5748-BBA3-0A5C48BE8543}">
+    <comment ref="T12" authorId="0" shapeId="0" xr:uid="{A5A840E0-3932-5748-BBA3-0A5C48BE8543}">
       <text>
         <r>
           <rPr>
@@ -647,7 +647,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0" xr:uid="{3964ECC7-EFA7-FE4E-BCAB-1FAB031AE713}">
+    <comment ref="K15" authorId="0" shapeId="0" xr:uid="{3964ECC7-EFA7-FE4E-BCAB-1FAB031AE713}">
       <text>
         <r>
           <rPr>
@@ -662,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P15" authorId="0" shapeId="0" xr:uid="{843BF8F3-40CE-FC47-8EB0-3E526B2D5828}">
+    <comment ref="Q15" authorId="0" shapeId="0" xr:uid="{843BF8F3-40CE-FC47-8EB0-3E526B2D5828}">
       <text>
         <r>
           <rPr>
@@ -677,7 +677,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R15" authorId="0" shapeId="0" xr:uid="{CD018D9D-1B5D-AA46-BAFD-0067251A6A27}">
+    <comment ref="S15" authorId="0" shapeId="0" xr:uid="{CD018D9D-1B5D-AA46-BAFD-0067251A6A27}">
       <text>
         <r>
           <rPr>
@@ -692,7 +692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{E4E5A782-6FE1-8948-8944-714A354CEF81}">
+    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{E4E5A782-6FE1-8948-8944-714A354CEF81}">
       <text>
         <r>
           <rPr>
@@ -707,7 +707,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{ADE8F02E-A7CA-CF4A-ACA3-2145C1515295}">
+    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{ADE8F02E-A7CA-CF4A-ACA3-2145C1515295}">
       <text>
         <r>
           <rPr>
@@ -722,7 +722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P19" authorId="0" shapeId="0" xr:uid="{AC0FF6FB-9B6D-D34D-8F64-52CF0D867F7D}">
+    <comment ref="Q19" authorId="0" shapeId="0" xr:uid="{AC0FF6FB-9B6D-D34D-8F64-52CF0D867F7D}">
       <text>
         <r>
           <rPr>
@@ -737,7 +737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0" xr:uid="{862D6CA5-6C4C-7D44-8AF2-F89B8269D485}">
+    <comment ref="R19" authorId="0" shapeId="0" xr:uid="{862D6CA5-6C4C-7D44-8AF2-F89B8269D485}">
       <text>
         <r>
           <rPr>
@@ -752,7 +752,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{BB386614-6EEE-784E-83C4-107ECAD3569D}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{BB386614-6EEE-784E-83C4-107ECAD3569D}">
       <text>
         <r>
           <rPr>
@@ -767,7 +767,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{0940F651-2726-2042-8A5A-EF5E44DBC144}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{0940F651-2726-2042-8A5A-EF5E44DBC144}">
       <text>
         <r>
           <rPr>
@@ -782,7 +782,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R20" authorId="0" shapeId="0" xr:uid="{1E4D8FB3-ADA8-554D-9CCE-E4877BC91E66}">
+    <comment ref="S20" authorId="0" shapeId="0" xr:uid="{1E4D8FB3-ADA8-554D-9CCE-E4877BC91E66}">
       <text>
         <r>
           <rPr>
@@ -799,7 +799,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N21" authorId="0" shapeId="0" xr:uid="{46ADBD5F-8263-074F-8E71-CB09CB8B9660}">
+    <comment ref="O21" authorId="0" shapeId="0" xr:uid="{46ADBD5F-8263-074F-8E71-CB09CB8B9660}">
       <text>
         <r>
           <rPr>
@@ -814,7 +814,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{C168EB99-C3D0-4C4B-9632-4C231DF9897D}">
+    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{C168EB99-C3D0-4C4B-9632-4C231DF9897D}">
       <text>
         <r>
           <rPr>
@@ -829,7 +829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G28" authorId="0" shapeId="0" xr:uid="{260FA5BE-787E-CC40-A6E2-850416D8FA2C}">
+    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{260FA5BE-787E-CC40-A6E2-850416D8FA2C}">
       <text>
         <r>
           <rPr>
@@ -844,7 +844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{1E85253D-58BE-2140-B80A-7C0A06565C5B}">
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{1E85253D-58BE-2140-B80A-7C0A06565C5B}">
       <text>
         <r>
           <rPr>
@@ -859,7 +859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K28" authorId="0" shapeId="0" xr:uid="{6B4FEF0F-7CFF-7F41-9E24-AC1695CB5261}">
+    <comment ref="L28" authorId="0" shapeId="0" xr:uid="{6B4FEF0F-7CFF-7F41-9E24-AC1695CB5261}">
       <text>
         <r>
           <rPr>
@@ -874,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0" xr:uid="{808AB7EA-D5E0-2A4F-A97F-5B9537C001EA}">
+    <comment ref="M28" authorId="0" shapeId="0" xr:uid="{808AB7EA-D5E0-2A4F-A97F-5B9537C001EA}">
       <text>
         <r>
           <rPr>
@@ -889,7 +889,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P28" authorId="0" shapeId="0" xr:uid="{945D855E-ECAE-9347-928D-063195A7E1CC}">
+    <comment ref="Q28" authorId="0" shapeId="0" xr:uid="{945D855E-ECAE-9347-928D-063195A7E1CC}">
       <text>
         <r>
           <rPr>
@@ -904,7 +904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0" xr:uid="{1116CE8B-DEB6-6B47-8FB6-EBD5ED3B4517}">
+    <comment ref="T28" authorId="0" shapeId="0" xr:uid="{1116CE8B-DEB6-6B47-8FB6-EBD5ED3B4517}">
       <text>
         <r>
           <rPr>
@@ -919,7 +919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{54502BD6-D4C4-4447-9804-6FFFB19D484D}">
+    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{54502BD6-D4C4-4447-9804-6FFFB19D484D}">
       <text>
         <r>
           <rPr>
@@ -934,7 +934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{2FB92A38-3A20-0341-8FD2-A9B54FF6D455}">
+    <comment ref="H31" authorId="0" shapeId="0" xr:uid="{2FB92A38-3A20-0341-8FD2-A9B54FF6D455}">
       <text>
         <r>
           <rPr>
@@ -949,7 +949,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J31" authorId="0" shapeId="0" xr:uid="{EC46B808-080C-F14C-A202-75FF1127699B}">
+    <comment ref="K31" authorId="0" shapeId="0" xr:uid="{EC46B808-080C-F14C-A202-75FF1127699B}">
       <text>
         <r>
           <rPr>
@@ -964,7 +964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P31" authorId="0" shapeId="0" xr:uid="{EB8DDB58-E7B2-A046-9959-32E6E59069F6}">
+    <comment ref="Q31" authorId="0" shapeId="0" xr:uid="{EB8DDB58-E7B2-A046-9959-32E6E59069F6}">
       <text>
         <r>
           <rPr>
@@ -979,7 +979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q31" authorId="0" shapeId="0" xr:uid="{EDEAC20C-9388-0142-86B5-AE43AE7D3E4A}">
+    <comment ref="R31" authorId="0" shapeId="0" xr:uid="{EDEAC20C-9388-0142-86B5-AE43AE7D3E4A}">
       <text>
         <r>
           <rPr>
@@ -994,7 +994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{4B4A21FB-EA0B-1B47-A43C-24D6A4429405}">
+    <comment ref="J33" authorId="0" shapeId="0" xr:uid="{4B4A21FB-EA0B-1B47-A43C-24D6A4429405}">
       <text>
         <r>
           <rPr>
@@ -1009,7 +1009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K33" authorId="0" shapeId="0" xr:uid="{3069C28B-1839-2D47-90A5-8D023B0A4E4B}">
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{3069C28B-1839-2D47-90A5-8D023B0A4E4B}">
       <text>
         <r>
           <rPr>
@@ -1024,7 +1024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N33" authorId="0" shapeId="0" xr:uid="{F741CAE5-2F99-084D-A836-C1D69A20572D}">
+    <comment ref="O33" authorId="0" shapeId="0" xr:uid="{F741CAE5-2F99-084D-A836-C1D69A20572D}">
       <text>
         <r>
           <rPr>
@@ -1039,7 +1039,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0" xr:uid="{700C8FF3-0005-5D4D-A162-53A4425C8CF4}">
+    <comment ref="R33" authorId="0" shapeId="0" xr:uid="{700C8FF3-0005-5D4D-A162-53A4425C8CF4}">
       <text>
         <r>
           <rPr>
@@ -1054,7 +1054,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R33" authorId="0" shapeId="0" xr:uid="{2F9A8713-7D9B-C941-ACDA-AECAD7E96D33}">
+    <comment ref="S33" authorId="0" shapeId="0" xr:uid="{2F9A8713-7D9B-C941-ACDA-AECAD7E96D33}">
       <text>
         <r>
           <rPr>
@@ -1074,7 +1074,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="611">
   <si>
     <t>Profesor(a):</t>
   </si>
@@ -3052,6 +3052,15 @@
   </si>
   <si>
     <t>jueves</t>
+  </si>
+  <si>
+    <t>carnet</t>
+  </si>
+  <si>
+    <t>Algoritmos y Programación</t>
+  </si>
+  <si>
+    <t>2425-2</t>
   </si>
 </sst>
 </file>
@@ -3070,7 +3079,7 @@
     <numFmt numFmtId="172" formatCode="0.0#"/>
     <numFmt numFmtId="173" formatCode="0&quot;/10&quot;"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3259,6 +3268,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3980,7 +3997,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4262,6 +4279,17 @@
     </xf>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4290,17 +4318,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10428,1252 +10448,1356 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:AB36"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="2" spans="1:28">
+      <c r="B1" s="133" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="3" spans="1:28">
+      <c r="B2" s="133" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="5" spans="1:28">
-      <c r="A5" s="145" t="s">
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
+      <c r="A5" s="141" t="s">
         <v>590</v>
       </c>
-      <c r="B5" s="145" t="s">
+      <c r="B5" s="141" t="s">
         <v>591</v>
       </c>
-      <c r="C5" s="145" t="s">
+      <c r="C5" s="141" t="s">
         <v>592</v>
       </c>
-      <c r="D5" s="145" t="s">
+      <c r="D5" s="141" t="s">
         <v>593</v>
       </c>
-      <c r="E5" s="145" t="s">
+      <c r="E5" s="156" t="s">
+        <v>608</v>
+      </c>
+      <c r="F5" s="141" t="s">
         <v>594</v>
       </c>
-      <c r="F5" s="145"/>
-      <c r="G5" s="145" t="s">
+      <c r="G5" s="141"/>
+      <c r="H5" s="141" t="s">
         <v>595</v>
       </c>
-      <c r="H5" s="145"/>
-      <c r="I5" s="145" t="s">
+      <c r="I5" s="141"/>
+      <c r="J5" s="141" t="s">
         <v>596</v>
       </c>
-      <c r="J5" s="145"/>
-      <c r="K5" s="145" t="s">
+      <c r="K5" s="141"/>
+      <c r="L5" s="141" t="s">
         <v>597</v>
       </c>
-      <c r="L5" s="145"/>
-      <c r="M5" s="145" t="s">
+      <c r="M5" s="141"/>
+      <c r="N5" s="141" t="s">
         <v>598</v>
       </c>
-      <c r="N5" s="145"/>
-      <c r="O5" s="145" t="s">
+      <c r="O5" s="141"/>
+      <c r="P5" s="141" t="s">
         <v>599</v>
       </c>
-      <c r="P5" s="145"/>
-      <c r="Q5" s="145" t="s">
+      <c r="Q5" s="141"/>
+      <c r="R5" s="141" t="s">
         <v>600</v>
       </c>
-      <c r="R5" s="145"/>
-      <c r="S5" s="145" t="s">
+      <c r="S5" s="141"/>
+      <c r="T5" s="141" t="s">
         <v>601</v>
       </c>
-      <c r="T5" s="145"/>
-      <c r="U5" s="145" t="s">
+      <c r="U5" s="141"/>
+      <c r="V5" s="141" t="s">
         <v>602</v>
       </c>
-      <c r="V5" s="145"/>
-      <c r="W5" s="145" t="s">
+      <c r="W5" s="141"/>
+      <c r="X5" s="141" t="s">
         <v>603</v>
       </c>
-      <c r="X5" s="145"/>
-      <c r="Y5" s="145" t="s">
+      <c r="Y5" s="141"/>
+      <c r="Z5" s="141" t="s">
         <v>604</v>
       </c>
-      <c r="Z5" s="145"/>
-      <c r="AA5" s="145" t="s">
+      <c r="AA5" s="141"/>
+      <c r="AB5" s="141" t="s">
         <v>605</v>
       </c>
-      <c r="AB5" s="145"/>
-    </row>
-    <row r="6" spans="1:28">
-      <c r="A6" s="145"/>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="148" t="s">
+      <c r="AC5" s="141"/>
+    </row>
+    <row r="6" spans="1:29">
+      <c r="A6" s="141"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="141"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="F6" s="148" t="s">
+      <c r="G6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="G6" s="148" t="s">
+      <c r="H6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="H6" s="148" t="s">
+      <c r="I6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="I6" s="148" t="s">
+      <c r="J6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="J6" s="148" t="s">
+      <c r="K6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="K6" s="148" t="s">
+      <c r="L6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="L6" s="148" t="s">
+      <c r="M6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="M6" s="148" t="s">
+      <c r="N6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="N6" s="148" t="s">
+      <c r="O6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="O6" s="148" t="s">
+      <c r="P6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="P6" s="148" t="s">
+      <c r="Q6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="Q6" s="148" t="s">
+      <c r="R6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="R6" s="148" t="s">
+      <c r="S6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="S6" s="148" t="s">
+      <c r="T6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="T6" s="148" t="s">
+      <c r="U6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="U6" s="148" t="s">
+      <c r="V6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="V6" s="148" t="s">
+      <c r="W6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="W6" s="148" t="s">
+      <c r="X6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="X6" s="148" t="s">
+      <c r="Y6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="Y6" s="148" t="s">
+      <c r="Z6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="Z6" s="148" t="s">
+      <c r="AA6" s="133" t="s">
         <v>607</v>
       </c>
-      <c r="AA6" s="148" t="s">
+      <c r="AB6" s="133" t="s">
         <v>606</v>
       </c>
-      <c r="AB6" s="148" t="s">
+      <c r="AC6" s="133" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
-      <c r="A7" s="146">
-        <v>1</v>
-      </c>
-      <c r="B7" s="146" t="s">
+    <row r="7" spans="1:29">
+      <c r="A7" s="131">
+        <v>1</v>
+      </c>
+      <c r="B7" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="146" t="s">
+      <c r="C7" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="146">
+      <c r="D7" s="131">
         <v>28410856</v>
       </c>
-      <c r="E7" s="149">
-        <v>1</v>
-      </c>
-      <c r="F7" s="149"/>
-      <c r="G7" s="149"/>
-      <c r="H7" s="149"/>
-      <c r="I7" s="149"/>
-      <c r="J7" s="149"/>
-      <c r="K7" s="149"/>
-      <c r="L7" s="149"/>
-      <c r="N7" s="149"/>
-      <c r="P7" s="149"/>
-      <c r="Q7" s="149"/>
-      <c r="R7" s="149"/>
-      <c r="S7" s="149"/>
-      <c r="T7" s="149"/>
-      <c r="X7" s="152"/>
-    </row>
-    <row r="8" spans="1:28">
-      <c r="A8" s="147">
+      <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="134">
+        <v>1</v>
+      </c>
+      <c r="G7" s="134"/>
+      <c r="H7" s="134"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="134"/>
+      <c r="M7" s="134"/>
+      <c r="O7" s="134"/>
+      <c r="Q7" s="134"/>
+      <c r="R7" s="134"/>
+      <c r="S7" s="134"/>
+      <c r="T7" s="134"/>
+      <c r="U7" s="134"/>
+      <c r="Y7" s="137"/>
+    </row>
+    <row r="8" spans="1:29">
+      <c r="A8" s="132">
         <v>2</v>
       </c>
-      <c r="B8" s="147" t="s">
+      <c r="B8" s="132" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="147" t="s">
+      <c r="C8" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="147">
+      <c r="D8" s="132">
         <v>30849611</v>
       </c>
-      <c r="E8" s="150">
-        <v>1</v>
-      </c>
-      <c r="F8" s="150"/>
-      <c r="G8" s="150">
+      <c r="E8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="135">
+        <v>1</v>
+      </c>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135">
         <v>2</v>
       </c>
-      <c r="H8" s="150"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="150"/>
-      <c r="K8" s="150"/>
-      <c r="L8" s="150"/>
-      <c r="N8" s="150"/>
-      <c r="P8" s="150"/>
-      <c r="Q8" s="150"/>
-      <c r="R8" s="150"/>
-      <c r="S8" s="150"/>
-      <c r="T8" s="150"/>
-      <c r="X8" s="154"/>
-    </row>
-    <row r="9" spans="1:28">
-      <c r="A9" s="146">
+      <c r="I8" s="135"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="135"/>
+      <c r="O8" s="135"/>
+      <c r="Q8" s="135"/>
+      <c r="R8" s="135"/>
+      <c r="S8" s="135"/>
+      <c r="T8" s="135"/>
+      <c r="U8" s="135"/>
+      <c r="Y8" s="139"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="131">
         <v>3</v>
       </c>
-      <c r="B9" s="146" t="s">
+      <c r="B9" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="146" t="s">
+      <c r="C9" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="146">
+      <c r="D9" s="131">
         <v>29666935</v>
       </c>
-      <c r="E9" s="151">
-        <v>1</v>
-      </c>
-      <c r="F9" s="151"/>
-      <c r="G9" s="151">
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="136">
+        <v>1</v>
+      </c>
+      <c r="G9" s="136"/>
+      <c r="H9" s="136">
         <v>5</v>
       </c>
-      <c r="H9" s="151"/>
-      <c r="I9" s="151">
+      <c r="I9" s="136"/>
+      <c r="J9" s="136">
         <v>3</v>
       </c>
-      <c r="J9" s="151"/>
-      <c r="K9" s="151">
+      <c r="K9" s="136"/>
+      <c r="L9" s="136">
         <v>3</v>
       </c>
-      <c r="L9" s="151"/>
-      <c r="N9" s="151">
+      <c r="M9" s="136"/>
+      <c r="O9" s="136">
         <v>3</v>
       </c>
-      <c r="P9" s="151"/>
-      <c r="Q9" s="151">
+      <c r="Q9" s="136"/>
+      <c r="R9" s="136">
         <v>3</v>
       </c>
-      <c r="R9" s="151">
-        <v>1</v>
-      </c>
-      <c r="S9" s="151"/>
-      <c r="T9" s="151">
-        <v>1</v>
-      </c>
-      <c r="X9" s="152"/>
-    </row>
-    <row r="10" spans="1:28">
-      <c r="A10" s="147">
+      <c r="S9" s="136">
+        <v>1</v>
+      </c>
+      <c r="T9" s="136"/>
+      <c r="U9" s="136">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="137"/>
+    </row>
+    <row r="10" spans="1:29">
+      <c r="A10" s="132">
         <v>4</v>
       </c>
-      <c r="B10" s="147" t="s">
+      <c r="B10" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="147" t="s">
+      <c r="C10" s="132" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="147">
+      <c r="D10" s="132">
         <v>30765878</v>
       </c>
-      <c r="E10" s="150">
-        <v>1</v>
-      </c>
-      <c r="F10" s="150">
+      <c r="E10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="135">
+        <v>1</v>
+      </c>
+      <c r="G10" s="135">
         <v>2</v>
       </c>
-      <c r="G10" s="150"/>
-      <c r="H10" s="150"/>
-      <c r="I10" s="150"/>
-      <c r="J10" s="150"/>
-      <c r="K10" s="150"/>
-      <c r="L10" s="150">
-        <v>1</v>
-      </c>
-      <c r="N10" s="150"/>
-      <c r="P10" s="150"/>
-      <c r="Q10" s="150"/>
-      <c r="R10" s="150"/>
-      <c r="S10" s="150"/>
-      <c r="T10" s="150"/>
-      <c r="X10" s="154"/>
-    </row>
-    <row r="11" spans="1:28">
-      <c r="A11" s="146">
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="135"/>
+      <c r="L10" s="135"/>
+      <c r="M10" s="135">
+        <v>1</v>
+      </c>
+      <c r="O10" s="135"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="135"/>
+      <c r="S10" s="135"/>
+      <c r="T10" s="135"/>
+      <c r="U10" s="135"/>
+      <c r="Y10" s="139"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="131">
         <v>5</v>
       </c>
-      <c r="B11" s="146" t="s">
+      <c r="B11" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="146" t="s">
+      <c r="C11" s="131" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="146">
+      <c r="D11" s="131">
         <v>32729082</v>
       </c>
-      <c r="E11" s="151"/>
-      <c r="F11" s="151"/>
-      <c r="G11" s="151"/>
-      <c r="H11" s="151"/>
-      <c r="I11" s="151">
+      <c r="E11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="136"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="136">
         <v>2</v>
       </c>
-      <c r="J11" s="109"/>
       <c r="K11" s="109"/>
       <c r="L11" s="109"/>
-      <c r="N11" s="109"/>
-      <c r="P11" s="109"/>
+      <c r="M11" s="109"/>
+      <c r="O11" s="109"/>
       <c r="Q11" s="109"/>
       <c r="R11" s="109"/>
       <c r="S11" s="109"/>
       <c r="T11" s="109"/>
-      <c r="X11" s="152"/>
-    </row>
-    <row r="12" spans="1:28">
-      <c r="A12" s="146">
+      <c r="U11" s="109"/>
+      <c r="Y11" s="137"/>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="131">
         <v>6</v>
       </c>
-      <c r="B12" s="147" t="s">
+      <c r="B12" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="147" t="s">
+      <c r="C12" s="132" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="147">
+      <c r="D12" s="132">
         <v>31071592</v>
       </c>
-      <c r="E12" s="150"/>
-      <c r="F12" s="150"/>
-      <c r="G12" s="150">
-        <v>1</v>
-      </c>
-      <c r="H12" s="150">
+      <c r="E12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135">
+        <v>1</v>
+      </c>
+      <c r="I12" s="135">
         <v>2</v>
       </c>
-      <c r="I12" s="150">
+      <c r="J12" s="135">
         <v>2</v>
       </c>
-      <c r="J12" s="150"/>
-      <c r="K12" s="150"/>
-      <c r="L12" s="150"/>
-      <c r="N12" s="150"/>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="150"/>
-      <c r="R12" s="150"/>
-      <c r="S12" s="154">
+      <c r="K12" s="135"/>
+      <c r="L12" s="135"/>
+      <c r="M12" s="135"/>
+      <c r="O12" s="135"/>
+      <c r="Q12" s="135"/>
+      <c r="R12" s="135"/>
+      <c r="S12" s="135"/>
+      <c r="T12" s="139">
         <v>2</v>
       </c>
-      <c r="T12" s="154">
-        <v>1</v>
-      </c>
-      <c r="X12" s="154"/>
-    </row>
-    <row r="13" spans="1:28">
-      <c r="A13" s="147">
+      <c r="U12" s="139">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="139"/>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="132">
         <v>7</v>
       </c>
-      <c r="B13" s="146" t="s">
+      <c r="B13" s="131" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="146" t="s">
+      <c r="C13" s="131" t="s">
         <v>76</v>
       </c>
-      <c r="D13" s="146">
+      <c r="D13" s="131">
         <v>32491310</v>
       </c>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
-      <c r="G13" s="151"/>
-      <c r="H13" s="151"/>
-      <c r="I13" s="151"/>
-      <c r="J13" s="151"/>
-      <c r="K13" s="151"/>
-      <c r="L13" s="151"/>
-      <c r="N13" s="151"/>
-      <c r="P13" s="151"/>
-      <c r="Q13" s="151"/>
-      <c r="R13" s="151"/>
-      <c r="S13" s="151"/>
-      <c r="T13" s="151"/>
-      <c r="X13" s="152"/>
-    </row>
-    <row r="14" spans="1:28">
-      <c r="A14" s="146">
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="136"/>
+      <c r="G13" s="136"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="136"/>
+      <c r="J13" s="136"/>
+      <c r="K13" s="136"/>
+      <c r="L13" s="136"/>
+      <c r="M13" s="136"/>
+      <c r="O13" s="136"/>
+      <c r="Q13" s="136"/>
+      <c r="R13" s="136"/>
+      <c r="S13" s="136"/>
+      <c r="T13" s="136"/>
+      <c r="U13" s="136"/>
+      <c r="Y13" s="137"/>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="131">
         <v>8</v>
       </c>
-      <c r="B14" s="147" t="s">
+      <c r="B14" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="147" t="s">
+      <c r="C14" s="132" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="147">
+      <c r="D14" s="132">
         <v>31988236</v>
       </c>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="150">
-        <v>1</v>
-      </c>
-      <c r="N14" s="150"/>
-      <c r="P14" s="150"/>
-      <c r="Q14" s="150"/>
-      <c r="R14" s="150"/>
-      <c r="S14" s="150"/>
-      <c r="T14" s="150"/>
-      <c r="X14" s="154"/>
-    </row>
-    <row r="15" spans="1:28">
-      <c r="A15" s="147">
+      <c r="E14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="135"/>
+      <c r="J14" s="135"/>
+      <c r="K14" s="135"/>
+      <c r="L14" s="135"/>
+      <c r="M14" s="135">
+        <v>1</v>
+      </c>
+      <c r="O14" s="135"/>
+      <c r="Q14" s="135"/>
+      <c r="R14" s="135"/>
+      <c r="S14" s="135"/>
+      <c r="T14" s="135"/>
+      <c r="U14" s="135"/>
+      <c r="Y14" s="139"/>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="132">
         <v>9</v>
       </c>
-      <c r="B15" s="146" t="s">
+      <c r="B15" s="131" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="146" t="s">
+      <c r="C15" s="131" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="146">
+      <c r="D15" s="131">
         <v>31112818</v>
       </c>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="151"/>
-      <c r="H15" s="151"/>
-      <c r="I15" s="151"/>
-      <c r="J15" s="152">
+      <c r="E15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="136"/>
+      <c r="J15" s="136"/>
+      <c r="K15" s="137">
         <v>2</v>
       </c>
-      <c r="K15" s="153"/>
-      <c r="L15" s="151">
-        <v>1</v>
-      </c>
-      <c r="N15" s="151"/>
-      <c r="P15" s="151">
+      <c r="L15" s="138"/>
+      <c r="M15" s="136">
+        <v>1</v>
+      </c>
+      <c r="O15" s="136"/>
+      <c r="Q15" s="136">
         <v>2</v>
       </c>
-      <c r="Q15" s="151"/>
-      <c r="R15" s="152">
+      <c r="R15" s="136"/>
+      <c r="S15" s="137">
         <v>2</v>
       </c>
-      <c r="S15" s="152"/>
-      <c r="T15" s="152"/>
-      <c r="X15" s="152"/>
-    </row>
-    <row r="16" spans="1:28">
-      <c r="A16" s="146">
+      <c r="T15" s="137"/>
+      <c r="U15" s="137"/>
+      <c r="Y15" s="137"/>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="131">
         <v>10</v>
       </c>
-      <c r="B16" s="147" t="s">
+      <c r="B16" s="132" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="147" t="s">
+      <c r="C16" s="132" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="147">
+      <c r="D16" s="132">
         <v>30030485</v>
       </c>
-      <c r="E16" s="150"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="150"/>
-      <c r="K16" s="150"/>
-      <c r="L16" s="150"/>
-      <c r="N16" s="150"/>
-      <c r="P16" s="150"/>
-      <c r="Q16" s="150"/>
-      <c r="R16" s="150"/>
-      <c r="S16" s="150"/>
-      <c r="T16" s="150"/>
-      <c r="X16" s="154">
+      <c r="E16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="135"/>
+      <c r="J16" s="135"/>
+      <c r="K16" s="135"/>
+      <c r="L16" s="135"/>
+      <c r="M16" s="135"/>
+      <c r="O16" s="135"/>
+      <c r="Q16" s="135"/>
+      <c r="R16" s="135"/>
+      <c r="S16" s="135"/>
+      <c r="T16" s="135"/>
+      <c r="U16" s="135"/>
+      <c r="Y16" s="139">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
-      <c r="A17" s="146">
+    <row r="17" spans="1:25">
+      <c r="A17" s="131">
         <v>11</v>
       </c>
-      <c r="B17" s="146" t="s">
+      <c r="B17" s="131" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="146" t="s">
+      <c r="C17" s="131" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="146">
+      <c r="D17" s="131">
         <v>30793086</v>
       </c>
-      <c r="E17" s="151"/>
-      <c r="F17" s="151"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="151"/>
-      <c r="J17" s="151"/>
-      <c r="K17" s="151"/>
-      <c r="L17" s="151"/>
-      <c r="N17" s="151"/>
-      <c r="P17" s="151"/>
-      <c r="Q17" s="151"/>
-      <c r="R17" s="151"/>
-      <c r="S17" s="151"/>
-      <c r="T17" s="151"/>
-      <c r="X17" s="152"/>
-    </row>
-    <row r="18" spans="1:24">
-      <c r="A18" s="147">
+      <c r="E17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="136"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="136"/>
+      <c r="K17" s="136"/>
+      <c r="L17" s="136"/>
+      <c r="M17" s="136"/>
+      <c r="O17" s="136"/>
+      <c r="Q17" s="136"/>
+      <c r="R17" s="136"/>
+      <c r="S17" s="136"/>
+      <c r="T17" s="136"/>
+      <c r="U17" s="136"/>
+      <c r="Y17" s="137"/>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="132">
         <v>12</v>
       </c>
-      <c r="B18" s="147" t="s">
+      <c r="B18" s="132" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="147" t="s">
+      <c r="C18" s="132" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="147">
+      <c r="D18" s="132">
         <v>32242412</v>
       </c>
-      <c r="E18" s="150"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="150"/>
-      <c r="K18" s="150">
-        <v>1</v>
-      </c>
-      <c r="L18" s="150"/>
-      <c r="N18" s="150">
-        <v>1</v>
-      </c>
-      <c r="P18" s="150"/>
-      <c r="Q18" s="150">
+      <c r="E18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="135"/>
+      <c r="K18" s="135"/>
+      <c r="L18" s="135">
+        <v>1</v>
+      </c>
+      <c r="M18" s="135"/>
+      <c r="O18" s="135">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="135"/>
+      <c r="R18" s="135">
         <v>3</v>
       </c>
-      <c r="R18" s="150">
-        <v>1</v>
-      </c>
-      <c r="S18" s="150">
-        <v>1</v>
-      </c>
-      <c r="T18" s="150"/>
-      <c r="X18" s="154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24">
-      <c r="A19" s="146">
+      <c r="S18" s="135">
+        <v>1</v>
+      </c>
+      <c r="T18" s="135">
+        <v>1</v>
+      </c>
+      <c r="U18" s="135"/>
+      <c r="Y18" s="139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="131">
         <v>13</v>
       </c>
-      <c r="B19" s="146" t="s">
+      <c r="B19" s="131" t="s">
         <v>94</v>
       </c>
-      <c r="C19" s="146" t="s">
+      <c r="C19" s="131" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="146">
+      <c r="D19" s="131">
         <v>30598031</v>
       </c>
-      <c r="E19" s="151"/>
-      <c r="F19" s="151"/>
-      <c r="G19" s="151">
+      <c r="E19" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="136"/>
+      <c r="G19" s="136"/>
+      <c r="H19" s="136">
         <v>2</v>
       </c>
-      <c r="H19" s="151"/>
-      <c r="I19" s="151">
+      <c r="I19" s="136"/>
+      <c r="J19" s="136">
         <v>2</v>
       </c>
-      <c r="J19" s="151"/>
-      <c r="K19" s="151"/>
-      <c r="L19" s="151">
+      <c r="K19" s="136"/>
+      <c r="L19" s="136"/>
+      <c r="M19" s="136">
         <v>2</v>
       </c>
-      <c r="N19" s="151"/>
-      <c r="P19" s="153">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="151">
+      <c r="O19" s="136"/>
+      <c r="Q19" s="138">
+        <v>1</v>
+      </c>
+      <c r="R19" s="136">
         <v>2</v>
       </c>
-      <c r="R19" s="151"/>
-      <c r="S19" s="151"/>
-      <c r="T19" s="151"/>
-      <c r="X19" s="152"/>
-    </row>
-    <row r="20" spans="1:24">
-      <c r="A20" s="147">
+      <c r="S19" s="136"/>
+      <c r="T19" s="136"/>
+      <c r="U19" s="136"/>
+      <c r="Y19" s="137"/>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" s="132">
         <v>14</v>
       </c>
-      <c r="B20" s="147" t="s">
+      <c r="B20" s="132" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="147" t="s">
+      <c r="C20" s="132" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="147">
+      <c r="D20" s="132">
         <v>31852058</v>
       </c>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150">
+      <c r="E20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="135">
         <v>3</v>
       </c>
-      <c r="I20" s="150">
+      <c r="J20" s="135">
         <v>2</v>
       </c>
-      <c r="J20" s="150">
-        <v>1</v>
-      </c>
-      <c r="K20" s="150">
-        <v>1</v>
-      </c>
-      <c r="L20" s="150">
-        <v>1</v>
-      </c>
-      <c r="N20" s="150"/>
-      <c r="P20" s="150"/>
-      <c r="Q20" s="150">
-        <v>1</v>
-      </c>
-      <c r="R20" s="150">
-        <v>1</v>
-      </c>
-      <c r="S20" s="150">
-        <v>1</v>
-      </c>
-      <c r="T20" s="150">
-        <v>1</v>
-      </c>
-      <c r="X20" s="154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24">
-      <c r="A21" s="146">
+      <c r="K20" s="135">
+        <v>1</v>
+      </c>
+      <c r="L20" s="135">
+        <v>1</v>
+      </c>
+      <c r="M20" s="135">
+        <v>1</v>
+      </c>
+      <c r="O20" s="135"/>
+      <c r="Q20" s="135"/>
+      <c r="R20" s="135">
+        <v>1</v>
+      </c>
+      <c r="S20" s="135">
+        <v>1</v>
+      </c>
+      <c r="T20" s="135">
+        <v>1</v>
+      </c>
+      <c r="U20" s="135">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" s="131">
         <v>15</v>
       </c>
-      <c r="B21" s="146" t="s">
+      <c r="B21" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="146" t="s">
+      <c r="C21" s="131" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="146">
+      <c r="D21" s="131">
         <v>30114012</v>
       </c>
-      <c r="E21" s="151">
+      <c r="E21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="136">
         <v>2</v>
       </c>
-      <c r="F21" s="151"/>
-      <c r="G21" s="151">
-        <v>1</v>
-      </c>
-      <c r="H21" s="151">
-        <v>1</v>
-      </c>
-      <c r="I21" s="151"/>
-      <c r="J21" s="151">
-        <v>1</v>
-      </c>
-      <c r="K21" s="151"/>
-      <c r="L21" s="151"/>
-      <c r="N21" s="151">
+      <c r="G21" s="136"/>
+      <c r="H21" s="136">
+        <v>1</v>
+      </c>
+      <c r="I21" s="136">
+        <v>1</v>
+      </c>
+      <c r="J21" s="136"/>
+      <c r="K21" s="136">
+        <v>1</v>
+      </c>
+      <c r="L21" s="136"/>
+      <c r="M21" s="136"/>
+      <c r="O21" s="136">
         <v>3</v>
       </c>
-      <c r="P21" s="151"/>
-      <c r="Q21" s="151"/>
-      <c r="R21" s="151">
-        <v>1</v>
-      </c>
-      <c r="S21" s="151">
-        <v>1</v>
-      </c>
-      <c r="T21" s="151"/>
-      <c r="X21" s="152"/>
-    </row>
-    <row r="22" spans="1:24">
-      <c r="A22" s="146">
+      <c r="Q21" s="136"/>
+      <c r="R21" s="136"/>
+      <c r="S21" s="136">
+        <v>1</v>
+      </c>
+      <c r="T21" s="136">
+        <v>1</v>
+      </c>
+      <c r="U21" s="136"/>
+      <c r="Y21" s="137"/>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="131">
         <v>16</v>
       </c>
-      <c r="B22" s="147" t="s">
+      <c r="B22" s="132" t="s">
         <v>151</v>
       </c>
-      <c r="C22" s="147" t="s">
+      <c r="C22" s="132" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="147">
+      <c r="D22" s="132">
         <v>26954417</v>
       </c>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="150"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="150"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="150"/>
-      <c r="N22" s="150"/>
-      <c r="P22" s="150"/>
-      <c r="Q22" s="150"/>
-      <c r="R22" s="150"/>
-      <c r="S22" s="150"/>
-      <c r="T22" s="150"/>
-      <c r="X22" s="154"/>
-    </row>
-    <row r="23" spans="1:24">
-      <c r="A23" s="147">
+      <c r="E22" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="135"/>
+      <c r="O22" s="135"/>
+      <c r="Q22" s="135"/>
+      <c r="R22" s="135"/>
+      <c r="S22" s="135"/>
+      <c r="T22" s="135"/>
+      <c r="U22" s="135"/>
+      <c r="Y22" s="139"/>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" s="132">
         <v>17</v>
       </c>
-      <c r="B23" s="146" t="s">
+      <c r="B23" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="C23" s="146" t="s">
+      <c r="C23" s="131" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="146">
+      <c r="D23" s="131">
         <v>31448943</v>
       </c>
-      <c r="E23" s="151">
+      <c r="E23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23" s="136">
         <v>2</v>
       </c>
-      <c r="F23" s="151">
-        <v>1</v>
-      </c>
-      <c r="G23" s="151"/>
-      <c r="H23" s="151"/>
-      <c r="I23" s="151">
+      <c r="G23" s="136">
+        <v>1</v>
+      </c>
+      <c r="H23" s="136"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="136">
         <v>2</v>
       </c>
-      <c r="J23" s="151"/>
-      <c r="K23" s="151"/>
-      <c r="L23" s="151"/>
-      <c r="N23" s="151"/>
-      <c r="P23" s="151"/>
-      <c r="Q23" s="151"/>
-      <c r="R23" s="151"/>
-      <c r="S23" s="151"/>
-      <c r="T23" s="151"/>
-      <c r="X23" s="152"/>
-    </row>
-    <row r="24" spans="1:24">
-      <c r="A24" s="146">
+      <c r="K23" s="136"/>
+      <c r="L23" s="136"/>
+      <c r="M23" s="136"/>
+      <c r="O23" s="136"/>
+      <c r="Q23" s="136"/>
+      <c r="R23" s="136"/>
+      <c r="S23" s="136"/>
+      <c r="T23" s="136"/>
+      <c r="U23" s="136"/>
+      <c r="Y23" s="137"/>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="131">
         <v>18</v>
       </c>
-      <c r="B24" s="147" t="s">
+      <c r="B24" s="132" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="147" t="s">
+      <c r="C24" s="132" t="s">
         <v>167</v>
       </c>
-      <c r="D24" s="147">
+      <c r="D24" s="132">
         <v>31423000</v>
       </c>
-      <c r="E24" s="150"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
-      <c r="I24" s="150"/>
-      <c r="J24" s="150">
-        <v>1</v>
-      </c>
-      <c r="K24" s="150"/>
-      <c r="L24" s="150"/>
-      <c r="N24" s="150"/>
-      <c r="P24" s="150">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="150"/>
-      <c r="R24" s="150"/>
-      <c r="S24" s="150">
-        <v>1</v>
-      </c>
-      <c r="T24" s="150"/>
-      <c r="X24" s="154"/>
-    </row>
-    <row r="25" spans="1:24">
-      <c r="A25" s="147">
+      <c r="E24" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="135">
+        <v>1</v>
+      </c>
+      <c r="L24" s="135"/>
+      <c r="M24" s="135"/>
+      <c r="O24" s="135"/>
+      <c r="Q24" s="135">
+        <v>1</v>
+      </c>
+      <c r="R24" s="135"/>
+      <c r="S24" s="135"/>
+      <c r="T24" s="135">
+        <v>1</v>
+      </c>
+      <c r="U24" s="135"/>
+      <c r="Y24" s="139"/>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="132">
         <v>19</v>
       </c>
-      <c r="B25" s="146" t="s">
+      <c r="B25" s="131" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="146" t="s">
+      <c r="C25" s="131" t="s">
         <v>176</v>
       </c>
-      <c r="D25" s="146">
+      <c r="D25" s="131">
         <v>31046285</v>
       </c>
-      <c r="E25" s="151"/>
-      <c r="F25" s="151"/>
-      <c r="G25" s="151"/>
-      <c r="H25" s="151"/>
-      <c r="I25" s="151"/>
-      <c r="J25" s="151"/>
-      <c r="K25" s="151"/>
-      <c r="L25" s="151"/>
-      <c r="N25" s="151">
-        <v>1</v>
-      </c>
-      <c r="P25" s="151"/>
-      <c r="Q25" s="151"/>
-      <c r="R25" s="151"/>
-      <c r="S25" s="151"/>
-      <c r="T25" s="151"/>
-      <c r="X25" s="152"/>
-    </row>
-    <row r="26" spans="1:24">
-      <c r="A26" s="146">
+      <c r="E25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="136"/>
+      <c r="L25" s="136"/>
+      <c r="M25" s="136"/>
+      <c r="O25" s="136">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="136"/>
+      <c r="R25" s="136"/>
+      <c r="S25" s="136"/>
+      <c r="T25" s="136"/>
+      <c r="U25" s="136"/>
+      <c r="Y25" s="137"/>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="131">
         <v>20</v>
       </c>
-      <c r="B26" s="147" t="s">
+      <c r="B26" s="132" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="147" t="s">
+      <c r="C26" s="132" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="147">
+      <c r="D26" s="132">
         <v>31255343</v>
       </c>
-      <c r="E26" s="150"/>
-      <c r="F26" s="150"/>
-      <c r="G26" s="150">
-        <v>1</v>
-      </c>
-      <c r="H26" s="150">
-        <v>1</v>
-      </c>
-      <c r="I26" s="150"/>
-      <c r="J26" s="150"/>
-      <c r="K26" s="150">
-        <v>1</v>
-      </c>
-      <c r="L26" s="150"/>
-      <c r="N26" s="150"/>
-      <c r="P26" s="150"/>
-      <c r="Q26" s="150"/>
-      <c r="R26" s="150"/>
-      <c r="S26" s="150"/>
-      <c r="T26" s="150"/>
-      <c r="X26" s="154"/>
-    </row>
-    <row r="27" spans="1:24">
-      <c r="A27" s="146">
+      <c r="E26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F26" s="135"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="135">
+        <v>1</v>
+      </c>
+      <c r="I26" s="135">
+        <v>1</v>
+      </c>
+      <c r="J26" s="135"/>
+      <c r="K26" s="135"/>
+      <c r="L26" s="135">
+        <v>1</v>
+      </c>
+      <c r="M26" s="135"/>
+      <c r="O26" s="135"/>
+      <c r="Q26" s="135"/>
+      <c r="R26" s="135"/>
+      <c r="S26" s="135"/>
+      <c r="T26" s="135"/>
+      <c r="U26" s="135"/>
+      <c r="Y26" s="139"/>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="131">
         <v>21</v>
       </c>
-      <c r="B27" s="146" t="s">
+      <c r="B27" s="131" t="s">
         <v>194</v>
       </c>
-      <c r="C27" s="146" t="s">
+      <c r="C27" s="131" t="s">
         <v>193</v>
       </c>
-      <c r="D27" s="146">
+      <c r="D27" s="131">
         <v>32401366</v>
       </c>
-      <c r="E27" s="151"/>
-      <c r="F27" s="151"/>
-      <c r="G27" s="151"/>
-      <c r="H27" s="151"/>
-      <c r="I27" s="151"/>
-      <c r="J27" s="151"/>
-      <c r="K27" s="151"/>
-      <c r="L27" s="151"/>
-      <c r="N27" s="151"/>
-      <c r="P27" s="151"/>
-      <c r="Q27" s="151"/>
-      <c r="R27" s="151"/>
-      <c r="S27" s="151"/>
-      <c r="T27" s="151"/>
-      <c r="X27" s="152">
+      <c r="E27" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="136"/>
+      <c r="G27" s="136"/>
+      <c r="H27" s="136"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="136"/>
+      <c r="L27" s="136"/>
+      <c r="M27" s="136"/>
+      <c r="O27" s="136"/>
+      <c r="Q27" s="136"/>
+      <c r="R27" s="136"/>
+      <c r="S27" s="136"/>
+      <c r="T27" s="136"/>
+      <c r="U27" s="136"/>
+      <c r="Y27" s="137">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
-      <c r="A28" s="147">
+    <row r="28" spans="1:25">
+      <c r="A28" s="132">
         <v>22</v>
       </c>
-      <c r="B28" s="147" t="s">
+      <c r="B28" s="132" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="147" t="s">
+      <c r="C28" s="132" t="s">
         <v>201</v>
       </c>
-      <c r="D28" s="147">
+      <c r="D28" s="132">
         <v>32121917</v>
       </c>
-      <c r="E28" s="150"/>
-      <c r="F28" s="150"/>
-      <c r="G28" s="150">
+      <c r="E28" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F28" s="135"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="135">
         <v>2</v>
       </c>
-      <c r="H28" s="150">
+      <c r="I28" s="135">
         <v>2</v>
       </c>
-      <c r="I28" s="150"/>
-      <c r="J28" s="150">
-        <v>1</v>
-      </c>
-      <c r="K28" s="150">
+      <c r="J28" s="135"/>
+      <c r="K28" s="135">
+        <v>1</v>
+      </c>
+      <c r="L28" s="135">
         <v>2</v>
       </c>
-      <c r="L28" s="150">
+      <c r="M28" s="135">
         <v>2</v>
       </c>
-      <c r="N28" s="150">
-        <v>1</v>
-      </c>
-      <c r="P28" s="150">
+      <c r="O28" s="135">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="135">
         <v>2</v>
       </c>
-      <c r="Q28" s="150"/>
-      <c r="R28" s="150">
-        <v>1</v>
-      </c>
-      <c r="S28" s="154">
+      <c r="R28" s="135"/>
+      <c r="S28" s="135">
+        <v>1</v>
+      </c>
+      <c r="T28" s="139">
         <v>2</v>
       </c>
-      <c r="T28" s="155"/>
-      <c r="X28" s="154">
+      <c r="U28" s="140"/>
+      <c r="Y28" s="139">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
-      <c r="A29" s="146">
+    <row r="29" spans="1:25">
+      <c r="A29" s="131">
         <v>23</v>
       </c>
-      <c r="B29" s="146" t="s">
+      <c r="B29" s="131" t="s">
         <v>210</v>
       </c>
-      <c r="C29" s="146" t="s">
+      <c r="C29" s="131" t="s">
         <v>209</v>
       </c>
-      <c r="D29" s="146">
+      <c r="D29" s="131">
         <v>33921124</v>
       </c>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
-      <c r="H29" s="151"/>
-      <c r="I29" s="151"/>
-      <c r="J29" s="151"/>
-      <c r="K29" s="151"/>
-      <c r="L29" s="151"/>
-      <c r="N29" s="151"/>
-      <c r="P29" s="151"/>
-      <c r="Q29" s="151">
-        <v>1</v>
-      </c>
-      <c r="R29" s="151">
-        <v>1</v>
-      </c>
-      <c r="S29" s="151"/>
-      <c r="T29" s="151"/>
-      <c r="X29" s="152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24">
-      <c r="A30" s="147">
+      <c r="E29" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F29" s="136"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="136"/>
+      <c r="I29" s="136"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="136"/>
+      <c r="L29" s="136"/>
+      <c r="M29" s="136"/>
+      <c r="O29" s="136"/>
+      <c r="Q29" s="136"/>
+      <c r="R29" s="136">
+        <v>1</v>
+      </c>
+      <c r="S29" s="136">
+        <v>1</v>
+      </c>
+      <c r="T29" s="136"/>
+      <c r="U29" s="136"/>
+      <c r="Y29" s="137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" s="132">
         <v>24</v>
       </c>
-      <c r="B30" s="147" t="s">
+      <c r="B30" s="132" t="s">
         <v>112</v>
       </c>
-      <c r="C30" s="147" t="s">
+      <c r="C30" s="132" t="s">
         <v>217</v>
       </c>
-      <c r="D30" s="147">
+      <c r="D30" s="132">
         <v>31703910</v>
       </c>
-      <c r="E30" s="150"/>
-      <c r="F30" s="150"/>
-      <c r="G30" s="150"/>
-      <c r="H30" s="150">
+      <c r="E30" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
+      <c r="I30" s="135">
         <v>2</v>
       </c>
-      <c r="I30" s="150"/>
-      <c r="J30" s="150"/>
-      <c r="K30" s="150"/>
-      <c r="L30" s="150"/>
-      <c r="N30" s="150"/>
-      <c r="P30" s="150"/>
-      <c r="Q30" s="150"/>
-      <c r="R30" s="150"/>
-      <c r="S30" s="150"/>
-      <c r="T30" s="150">
-        <v>1</v>
-      </c>
-      <c r="X30" s="154"/>
-    </row>
-    <row r="31" spans="1:24">
-      <c r="A31" s="146">
+      <c r="J30" s="135"/>
+      <c r="K30" s="135"/>
+      <c r="L30" s="135"/>
+      <c r="M30" s="135"/>
+      <c r="O30" s="135"/>
+      <c r="Q30" s="135"/>
+      <c r="R30" s="135"/>
+      <c r="S30" s="135"/>
+      <c r="T30" s="135"/>
+      <c r="U30" s="135">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="139"/>
+    </row>
+    <row r="31" spans="1:25">
+      <c r="A31" s="131">
         <v>25</v>
       </c>
-      <c r="B31" s="146" t="s">
+      <c r="B31" s="131" t="s">
         <v>226</v>
       </c>
-      <c r="C31" s="146" t="s">
+      <c r="C31" s="131" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="146">
+      <c r="D31" s="131">
         <v>32122110</v>
       </c>
-      <c r="E31" s="151">
-        <v>1</v>
-      </c>
-      <c r="F31" s="151"/>
-      <c r="G31" s="151">
+      <c r="E31" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F31" s="136">
+        <v>1</v>
+      </c>
+      <c r="G31" s="136"/>
+      <c r="H31" s="136">
         <v>2</v>
       </c>
-      <c r="H31" s="151"/>
-      <c r="I31" s="151"/>
-      <c r="J31" s="152">
+      <c r="I31" s="136"/>
+      <c r="J31" s="136"/>
+      <c r="K31" s="137">
         <v>2</v>
       </c>
-      <c r="K31" s="153"/>
-      <c r="L31" s="153"/>
-      <c r="N31" s="153"/>
-      <c r="P31" s="151">
+      <c r="L31" s="138"/>
+      <c r="M31" s="138"/>
+      <c r="O31" s="138"/>
+      <c r="Q31" s="136">
         <v>2</v>
       </c>
-      <c r="Q31" s="151">
+      <c r="R31" s="136">
         <v>2</v>
       </c>
-      <c r="R31" s="151"/>
-      <c r="S31" s="151"/>
-      <c r="T31" s="151"/>
-      <c r="X31" s="152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24">
-      <c r="A32" s="146">
+      <c r="S31" s="136"/>
+      <c r="T31" s="136"/>
+      <c r="U31" s="136"/>
+      <c r="Y31" s="137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25">
+      <c r="A32" s="131">
         <v>26</v>
       </c>
-      <c r="B32" s="147" t="s">
+      <c r="B32" s="132" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="147" t="s">
+      <c r="C32" s="132" t="s">
         <v>234</v>
       </c>
-      <c r="D32" s="147">
+      <c r="D32" s="132">
         <v>30720123</v>
       </c>
-      <c r="E32" s="150"/>
-      <c r="F32" s="150"/>
-      <c r="G32" s="150"/>
-      <c r="H32" s="150"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="150"/>
-      <c r="K32" s="150"/>
-      <c r="L32" s="150"/>
-      <c r="N32" s="150"/>
-      <c r="P32" s="150"/>
-      <c r="Q32" s="150"/>
-      <c r="R32" s="150"/>
-      <c r="S32" s="150"/>
-      <c r="T32" s="150"/>
-      <c r="X32" s="154"/>
-    </row>
-    <row r="33" spans="1:24">
-      <c r="A33" s="147">
+      <c r="E32" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F32" s="135"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="135"/>
+      <c r="I32" s="135"/>
+      <c r="J32" s="135"/>
+      <c r="K32" s="135"/>
+      <c r="L32" s="135"/>
+      <c r="M32" s="135"/>
+      <c r="O32" s="135"/>
+      <c r="Q32" s="135"/>
+      <c r="R32" s="135"/>
+      <c r="S32" s="135"/>
+      <c r="T32" s="135"/>
+      <c r="U32" s="135"/>
+      <c r="Y32" s="139"/>
+    </row>
+    <row r="33" spans="1:25">
+      <c r="A33" s="132">
         <v>27</v>
       </c>
-      <c r="B33" s="146" t="s">
+      <c r="B33" s="131" t="s">
         <v>243</v>
       </c>
-      <c r="C33" s="146" t="s">
+      <c r="C33" s="131" t="s">
         <v>242</v>
       </c>
-      <c r="D33" s="146">
+      <c r="D33" s="131">
         <v>29895575</v>
       </c>
-      <c r="E33" s="151"/>
-      <c r="F33" s="151"/>
-      <c r="G33" s="151"/>
-      <c r="H33" s="151"/>
-      <c r="I33" s="151">
+      <c r="E33" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F33" s="136"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="136"/>
+      <c r="I33" s="136"/>
+      <c r="J33" s="136">
         <v>2</v>
       </c>
-      <c r="J33" s="151"/>
-      <c r="K33" s="151">
+      <c r="K33" s="136"/>
+      <c r="L33" s="136">
         <v>2</v>
       </c>
-      <c r="L33" s="151">
-        <v>1</v>
-      </c>
-      <c r="N33" s="151">
+      <c r="M33" s="136">
+        <v>1</v>
+      </c>
+      <c r="O33" s="136">
         <v>2</v>
       </c>
-      <c r="P33" s="151"/>
-      <c r="Q33" s="151">
+      <c r="Q33" s="136"/>
+      <c r="R33" s="136">
         <v>2</v>
       </c>
-      <c r="R33" s="149">
+      <c r="S33" s="134">
         <v>2</v>
       </c>
-      <c r="S33" s="149"/>
-      <c r="T33" s="149"/>
-      <c r="X33" s="152"/>
-    </row>
-    <row r="34" spans="1:24">
-      <c r="A34" s="146">
+      <c r="T33" s="134"/>
+      <c r="U33" s="134"/>
+      <c r="Y33" s="137"/>
+    </row>
+    <row r="34" spans="1:25">
+      <c r="A34" s="131">
         <v>28</v>
       </c>
-      <c r="B34" s="147" t="s">
+      <c r="B34" s="132" t="s">
         <v>252</v>
       </c>
-      <c r="C34" s="147" t="s">
+      <c r="C34" s="132" t="s">
         <v>251</v>
       </c>
-      <c r="D34" s="147">
+      <c r="D34" s="132">
         <v>31615220</v>
       </c>
-      <c r="E34" s="150"/>
-      <c r="F34" s="150"/>
-      <c r="G34" s="150"/>
-      <c r="H34" s="150"/>
-      <c r="I34" s="150"/>
-      <c r="J34" s="150"/>
-      <c r="K34" s="150"/>
-      <c r="L34" s="150"/>
-      <c r="N34" s="150"/>
-      <c r="P34" s="150"/>
-      <c r="Q34" s="150"/>
-      <c r="R34" s="150"/>
-      <c r="S34" s="150"/>
-      <c r="T34" s="150"/>
-      <c r="X34" s="154"/>
-    </row>
-    <row r="35" spans="1:24">
-      <c r="A35" s="147">
+      <c r="E34" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="135"/>
+      <c r="K34" s="135"/>
+      <c r="L34" s="135"/>
+      <c r="M34" s="135"/>
+      <c r="O34" s="135"/>
+      <c r="Q34" s="135"/>
+      <c r="R34" s="135"/>
+      <c r="S34" s="135"/>
+      <c r="T34" s="135"/>
+      <c r="U34" s="135"/>
+      <c r="Y34" s="139"/>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" s="132">
         <v>29</v>
       </c>
-      <c r="B35" s="146" t="s">
+      <c r="B35" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="146" t="s">
+      <c r="C35" s="131" t="s">
         <v>260</v>
       </c>
-      <c r="D35" s="146">
+      <c r="D35" s="131">
         <v>30022208</v>
       </c>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151">
-        <v>1</v>
-      </c>
-      <c r="G35" s="151"/>
-      <c r="H35" s="151"/>
-      <c r="I35" s="151"/>
-      <c r="J35" s="151"/>
-      <c r="K35" s="151"/>
-      <c r="L35" s="151">
+      <c r="E35" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F35" s="136"/>
+      <c r="G35" s="136">
+        <v>1</v>
+      </c>
+      <c r="H35" s="136"/>
+      <c r="I35" s="136"/>
+      <c r="J35" s="136"/>
+      <c r="K35" s="136"/>
+      <c r="L35" s="136"/>
+      <c r="M35" s="136">
         <v>2</v>
       </c>
-      <c r="N35" s="151"/>
-      <c r="P35" s="151"/>
-      <c r="Q35" s="151">
-        <v>1</v>
-      </c>
-      <c r="R35" s="151"/>
-      <c r="S35" s="151"/>
-      <c r="T35" s="151"/>
-      <c r="X35" s="152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24">
-      <c r="A36" s="146">
+      <c r="O35" s="136"/>
+      <c r="Q35" s="136"/>
+      <c r="R35" s="136">
+        <v>1</v>
+      </c>
+      <c r="S35" s="136"/>
+      <c r="T35" s="136"/>
+      <c r="U35" s="136"/>
+      <c r="Y35" s="137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
+      <c r="A36" s="131">
         <v>30</v>
       </c>
-      <c r="B36" s="147" t="s">
+      <c r="B36" s="132" t="s">
         <v>268</v>
       </c>
-      <c r="C36" s="147" t="s">
+      <c r="C36" s="132" t="s">
         <v>267</v>
       </c>
-      <c r="D36" s="147">
+      <c r="D36" s="132">
         <v>31963201</v>
       </c>
-      <c r="E36" s="150"/>
-      <c r="F36" s="150"/>
-      <c r="G36" s="150"/>
-      <c r="H36" s="150"/>
-      <c r="I36" s="150"/>
-      <c r="J36" s="150">
-        <v>1</v>
-      </c>
-      <c r="K36" s="150"/>
-      <c r="L36" s="150"/>
-      <c r="N36" s="150"/>
-      <c r="P36" s="150"/>
-      <c r="Q36" s="150">
-        <v>1</v>
-      </c>
-      <c r="R36" s="150"/>
-      <c r="S36" s="150"/>
-      <c r="T36" s="150"/>
-      <c r="X36" s="154"/>
+      <c r="E36" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="135"/>
+      <c r="K36" s="135">
+        <v>1</v>
+      </c>
+      <c r="L36" s="135"/>
+      <c r="M36" s="135"/>
+      <c r="O36" s="135"/>
+      <c r="Q36" s="135"/>
+      <c r="R36" s="135">
+        <v>1</v>
+      </c>
+      <c r="S36" s="135"/>
+      <c r="T36" s="135"/>
+      <c r="U36" s="135"/>
+      <c r="Y36" s="139"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <phoneticPr fontId="31" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13685,7 +13809,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="142" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="15" t="s">
@@ -13703,12 +13827,12 @@
       <c r="F1" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="G1" s="131" t="s">
+      <c r="G1" s="142" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="132"/>
+      <c r="A2" s="143"/>
       <c r="B2" s="17" t="s">
         <v>293</v>
       </c>
@@ -13724,7 +13848,7 @@
       <c r="F2" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="132"/>
+      <c r="G2" s="143"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -15097,28 +15221,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="146" t="s">
         <v>326</v>
       </c>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="138" t="s">
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="149" t="s">
         <v>291</v>
       </c>
-      <c r="J1" s="139"/>
-      <c r="K1" s="140" t="s">
+      <c r="J1" s="150"/>
+      <c r="K1" s="151" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="134"/>
+      <c r="A2" s="145"/>
       <c r="B2" s="37" t="s">
         <v>327</v>
       </c>
@@ -15146,7 +15270,7 @@
       <c r="J2" s="38" t="s">
         <v>335</v>
       </c>
-      <c r="K2" s="141"/>
+      <c r="K2" s="152"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="39"/>
@@ -16467,41 +16591,41 @@
       <c r="C1" s="55"/>
       <c r="D1" s="55"/>
       <c r="E1" s="55"/>
-      <c r="F1" s="142" t="s">
+      <c r="F1" s="153" t="s">
         <v>347</v>
       </c>
-      <c r="G1" s="145"/>
-      <c r="H1" s="145"/>
-      <c r="I1" s="143"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="154"/>
       <c r="J1" s="55"/>
-      <c r="K1" s="142" t="s">
+      <c r="K1" s="153" t="s">
         <v>348</v>
       </c>
-      <c r="L1" s="145"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="144" t="s">
+      <c r="L1" s="141"/>
+      <c r="M1" s="154"/>
+      <c r="N1" s="155" t="s">
         <v>349</v>
       </c>
-      <c r="O1" s="145"/>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="142" t="s">
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="153" t="s">
         <v>350</v>
       </c>
-      <c r="R1" s="145"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="144" t="s">
+      <c r="R1" s="141"/>
+      <c r="S1" s="154"/>
+      <c r="T1" s="155" t="s">
         <v>351</v>
       </c>
-      <c r="U1" s="145"/>
-      <c r="V1" s="145"/>
-      <c r="W1" s="142" t="s">
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="153" t="s">
         <v>352</v>
       </c>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="144" t="s">
+      <c r="X1" s="154"/>
+      <c r="Y1" s="155" t="s">
         <v>353</v>
       </c>
-      <c r="Z1" s="143"/>
+      <c r="Z1" s="154"/>
       <c r="AA1" s="56"/>
       <c r="AB1" s="56"/>
     </row>

--- a/Datos Tesis Upstream/Algoritmos y Programacion/2425-2/Partic.Alg 2425-2 Secc. 2.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2425-2/Partic.Alg 2425-2 Secc. 2.xlsx
@@ -25,6 +25,7 @@
     <sheet name="Tareas" sheetId="10" r:id="rId10"/>
     <sheet name="Xtra" sheetId="11" r:id="rId11"/>
     <sheet name="Estandar" sheetId="12" r:id="rId12"/>
+    <sheet name="Cronograma" sheetId="13" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -11805,6 +11806,372 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin_clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">repaso</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>

--- a/Datos Tesis Upstream/Algoritmos y Programacion/2425-2/Partic.Alg 2425-2 Secc. 2.xlsx
+++ b/Datos Tesis Upstream/Algoritmos y Programacion/2425-2/Partic.Alg 2425-2 Secc. 2.xlsx
@@ -12008,7 +12008,7 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -12073,7 +12073,7 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
